--- a/math/01认识数.xlsx
+++ b/math/01认识数.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zimu/Documents/data-analytics/math/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40285256-EBDE-9341-8A78-71756DD831CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2921E18-CF55-CA41-AB4A-C60200694CAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{0D99BAC9-C8CF-7149-9DC9-A5E5FDA31523}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>

--- a/math/01认识数.xlsx
+++ b/math/01认识数.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zimu/Documents/data-analytics/math/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2921E18-CF55-CA41-AB4A-C60200694CAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5A0AD14-6483-BF44-B77D-029CEC8D4642}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{0D99BAC9-C8CF-7149-9DC9-A5E5FDA31523}"/>
   </bookViews>
